--- a/dados/excel/municipio_cargo.xlsx
+++ b/dados/excel/municipio_cargo.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>2270</v>
+        <v>2746</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>3036582.75</v>
+        <v>5784035.99</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1337.7</v>
+        <v>2106.35</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1416.64</v>
+        <v>2572.32</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>95.52</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="3">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>2102</v>
+        <v>2165</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>27996123.24</v>
+        <v>28482602.03</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>13318.8</v>
+        <v>13155.94</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>12648.2</v>
+        <v>12503.93</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>96.48</v>
+        <v>96.26000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -911,19 +911,19 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>1704</v>
+        <v>1700</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>8504264.5</v>
+        <v>8534115.73</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>4990.77</v>
+        <v>5020.07</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4722.97</v>
+        <v>4778.01</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>92.68000000000001</v>
+        <v>92.67</v>
       </c>
     </row>
     <row r="5">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>5119679</v>
+        <v>5110344.33</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>7768.86</v>
+        <v>7790.16</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>7270.99</v>
+        <v>7336.12</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>79.06</v>
+        <v>78.95999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>3136152.65</v>
+        <v>3278371.58</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>5733.37</v>
+        <v>5812.72</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4599.99</v>
+        <v>4876.53</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>96.68000000000001</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2768421.32</v>
+        <v>2793032.03</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>5471.19</v>
+        <v>5530.76</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>4599.26</v>
+        <v>4587.47</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>59.15</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="8">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>514858.48</v>
+        <v>490210.8</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1059.38</v>
+        <v>1012.83</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>77.84999999999999</v>
+        <v>76.51000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1049,13 +1049,13 @@
         <v>445</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>2800537.56</v>
+        <v>2974119.61</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>6293.34</v>
+        <v>6683.41</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>5385.33</v>
+        <v>5569.57</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>73.53</v>
@@ -1073,19 +1073,19 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2591367.64</v>
+        <v>2545676.7</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>7599.32</v>
+        <v>7553.94</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>6553.81</v>
+        <v>6526.29</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>19.47</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="11">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>6573716.12</v>
+        <v>6269486.7</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>22985.02</v>
+        <v>22153.66</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>18885.35</v>
+        <v>18601.17</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>46.26</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="12">
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>4468885.97</v>
+        <v>4386179.21</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>16674.95</v>
+        <v>16245.11</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>14938.03</v>
+        <v>13918.4</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>88.81</v>
       </c>
     </row>
     <row r="13">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>3081324.39</v>
+        <v>3366449.14</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>11943.12</v>
+        <v>12997.87</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>11993.66</v>
+        <v>12184.47</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>63.81</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="14">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1058446.85</v>
+        <v>1062205.79</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>4355.75</v>
+        <v>4425.86</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>4183.54</v>
+        <v>4156.02</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>63.6</v>
+        <v>62.71</v>
       </c>
     </row>
     <row r="15">
@@ -1204,23 +1204,23 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>SECRETARIO DE ESCOLA</t>
+          <t>AGENTE COMUNITARIO DE SAUDE</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>829711.36</v>
+        <v>770617.35</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>5568.53</v>
+        <v>5137.45</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>5240.32</v>
+        <v>5167.27</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>56.08</v>
+        <v>90.54000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1231,23 +1231,23 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>AGENTE COMUNITARIO DE SAUDE</t>
+          <t>SECRETARIO DE ESCOLA</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>716563.3199999999</v>
+        <v>834860.13</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>4874.58</v>
+        <v>5640.95</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>5194.79</v>
+        <v>5212.8</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>90.34</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="17">
@@ -1258,23 +1258,23 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>MOTORISTA</t>
+          <t>DIRETOR DE ESCOLA</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>987941.96</v>
+        <v>2786952.59</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>6908.69</v>
+        <v>18830.76</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>6410.59</v>
+        <v>16466.09</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>4.93</v>
+        <v>80.41</v>
       </c>
     </row>
     <row r="18">
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>DIRETOR DE ESCOLA</t>
+          <t>MOTORISTA</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2726024.44</v>
+        <v>956452.5699999999</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>19471.6</v>
+        <v>6783.35</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>17583.48</v>
+        <v>6360.98</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>82.14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1312,23 +1312,23 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>MEDICO I 100H</t>
+          <t>ASSESSOR DE GABINETE</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>1853771.62</v>
+        <v>1826714.01</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>15071.31</v>
+        <v>14731.56</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>13353.68</v>
+        <v>15452.79</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>63.11</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="20">
@@ -1339,23 +1339,23 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ASSESSOR DE GABINETE</t>
+          <t>MEDICO I 100H</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1801028.78</v>
+        <v>2097445.89</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>15008.57</v>
+        <v>17192.18</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>15480.31</v>
+        <v>14036.94</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>47.06</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="21">
@@ -1373,13 +1373,13 @@
         <v>118</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>1975595.03</v>
+        <v>2084613.24</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>16742.33</v>
+        <v>17666.21</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>15844.78</v>
+        <v>15817.26</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>63.79</v>
